--- a/data/trans_orig/IP16B10-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP16B10-Provincia-trans_orig.xlsx
@@ -6147,7 +6147,7 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1604</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4608</t>
+          <t>4390</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6265,7 +6265,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2493</t>
+          <t>2578</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6300,7 +6300,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2786</t>
+          <t>3004</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6315,7 +6315,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>40,62%</t>
         </is>
       </c>
     </row>
@@ -9161,7 +9161,7 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>1327</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
@@ -9176,7 +9176,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -9279,7 +9279,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2515</t>
+          <t>2497</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9294,7 +9294,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>65,3%</t>
         </is>
       </c>
     </row>
